--- a/TravelTour/캠핑준비.xlsx
+++ b/TravelTour/캠핑준비.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\01_Repo\01_doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\01_Repo\01_doc\TravelTour\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F20B28-58D4-4D57-AB1E-8AE2E70D73B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5162059-B15C-4DC1-B040-CC0EA4B114C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B35C64D8-44DB-4A7D-B642-3EC43ECC7117}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="126">
   <si>
     <t>육류</t>
   </si>
@@ -293,10 +293,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>의류</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>핸드폰 충전기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -344,10 +340,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>소주</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>와인</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -368,10 +360,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>김치</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>라면</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -380,10 +368,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>마스크</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>콩나물</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -392,26 +376,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>식용유</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>감자,고구마</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>칼, 도마, 가위, 집게</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>야채류</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>구이용 고기류</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>토치(가스)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -452,10 +424,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>미니 경광등</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>구매(필수)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -496,10 +464,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>수납백(보스턴)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -517,6 +481,38 @@
   </si>
   <si>
     <t>건조대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미니 경광등(스트링LED)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>칼, 도마, 가위, 집게, 호일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소주(막걸리)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김치,반찬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>식용유(올리브)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>의류, 모자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>노트북</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구이용(고기,생선,새우)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -640,9 +636,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -650,7 +643,12 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -978,11 +976,11 @@
     <col min="8" max="8" width="22.19921875" customWidth="1"/>
     <col min="9" max="9" width="4.296875" customWidth="1"/>
     <col min="10" max="10" width="8.796875" customWidth="1"/>
-    <col min="11" max="11" width="5.19921875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.59765625" customWidth="1"/>
+    <col min="11" max="11" width="5.19921875" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.5" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="4.296875" customWidth="1"/>
     <col min="14" max="14" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.19921875" style="3" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="13.69921875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="10.19921875" style="3" customWidth="1"/>
     <col min="19" max="20" width="4.296875" customWidth="1"/>
@@ -1030,483 +1028,441 @@
       </c>
       <c r="Q2" s="8"/>
       <c r="R2" s="7" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="D3" s="10" t="s">
+      <c r="C3" s="17"/>
+      <c r="D3" s="9" t="s">
         <v>29</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G3" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="H3" s="14" t="s">
+      <c r="G3" s="17"/>
+      <c r="H3" s="15" t="s">
         <v>48</v>
       </c>
       <c r="J3" t="s">
-        <v>73</v>
-      </c>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10" t="s">
-        <v>75</v>
+        <v>72</v>
+      </c>
+      <c r="K3" s="17"/>
+      <c r="L3" s="9" t="s">
+        <v>74</v>
       </c>
       <c r="N3" t="s">
         <v>64</v>
       </c>
-      <c r="O3" s="10"/>
-      <c r="P3" s="10" t="s">
+      <c r="O3" s="17"/>
+      <c r="P3" s="9" t="s">
         <v>65</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="S3" s="1"/>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.4">
-      <c r="C4" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="D4" s="11" t="s">
+      <c r="C4" s="17"/>
+      <c r="D4" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="H4" s="10" t="s">
+      <c r="G4" s="17"/>
+      <c r="H4" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="O4" s="10"/>
-      <c r="P4" s="10" t="s">
+      <c r="K4" s="17"/>
+      <c r="L4" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="O4" s="17"/>
+      <c r="P4" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="S4" s="2"/>
+    </row>
+    <row r="5" spans="2:19" x14ac:dyDescent="0.4">
+      <c r="C5" s="17"/>
+      <c r="D5" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" s="17"/>
+      <c r="H5" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="K5" s="17"/>
+      <c r="L5" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="O5" s="17"/>
+      <c r="P5" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="R5" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="R4" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="S4" s="2"/>
-    </row>
-    <row r="5" spans="2:19" x14ac:dyDescent="0.4">
-      <c r="C5" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="O5" s="10"/>
-      <c r="P5" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="R5" s="3" t="s">
-        <v>108</v>
-      </c>
       <c r="S5" s="4"/>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.4">
-      <c r="C6" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="D6" s="10" t="s">
+      <c r="C6" s="17"/>
+      <c r="D6" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10" t="s">
+      <c r="K6" s="17"/>
+      <c r="L6" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="O6" s="17"/>
+      <c r="P6" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="S6" s="6"/>
+    </row>
+    <row r="7" spans="2:19" x14ac:dyDescent="0.4">
+      <c r="C7" s="17"/>
+      <c r="D7" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="K7" s="17"/>
+      <c r="L7" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="O7" s="17"/>
+      <c r="P7" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="R7" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="S7" s="5"/>
+    </row>
+    <row r="8" spans="2:19" x14ac:dyDescent="0.4">
+      <c r="C8" s="17"/>
+      <c r="D8" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="K8" s="17"/>
+      <c r="L8" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="O6" s="10"/>
-      <c r="P6" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="R6" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="S6" s="6"/>
-    </row>
-    <row r="7" spans="2:19" x14ac:dyDescent="0.4">
-      <c r="C7" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="O7" s="10"/>
-      <c r="P7" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="R7" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="S7" s="5"/>
-    </row>
-    <row r="8" spans="2:19" x14ac:dyDescent="0.4">
-      <c r="C8" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="O8" s="10"/>
-      <c r="P8" s="10" t="s">
-        <v>78</v>
+      <c r="O8" s="17"/>
+      <c r="P8" s="9" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="2:19" x14ac:dyDescent="0.4">
-      <c r="C9" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="D9" s="10" t="s">
+      <c r="C9" s="17"/>
+      <c r="D9" s="9" t="s">
         <v>38</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="G9" s="9"/>
-      <c r="H9" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="O9" s="10"/>
-      <c r="P9" s="10" t="s">
+      <c r="G9" s="17"/>
+      <c r="H9" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="K9" s="17"/>
+      <c r="L9" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="O9" s="17"/>
+      <c r="P9" s="9" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="10" spans="2:19" x14ac:dyDescent="0.4">
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="17"/>
+      <c r="D10" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G10" s="17"/>
+      <c r="H10" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="K10" s="17"/>
+      <c r="L10" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="O10" s="17"/>
+      <c r="P10" s="9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="2:19" x14ac:dyDescent="0.4">
+      <c r="G11" s="17"/>
+      <c r="H11" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="K11" s="17"/>
+      <c r="L11" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="D10" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="O10" s="10"/>
-      <c r="P10" s="10" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="11" spans="2:19" x14ac:dyDescent="0.4">
-      <c r="G11" s="9"/>
-      <c r="H11" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="O11" s="10"/>
-      <c r="P11" s="17" t="s">
-        <v>103</v>
+      <c r="O11" s="17"/>
+      <c r="P11" s="9" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="10" t="s">
+      <c r="C12" s="17"/>
+      <c r="D12" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="G12" s="9"/>
-      <c r="H12" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10" t="s">
-        <v>90</v>
+      <c r="G12" s="17"/>
+      <c r="H12" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="K12" s="17"/>
+      <c r="L12" s="9" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="2:19" x14ac:dyDescent="0.4">
-      <c r="C13" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="D13" s="10" t="s">
+      <c r="C13" s="17"/>
+      <c r="D13" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10" t="s">
-        <v>91</v>
+      <c r="G13" s="17"/>
+      <c r="H13" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="K13" s="17"/>
+      <c r="L13" s="9" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.4">
-      <c r="C14" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="G14" s="9"/>
-      <c r="H14" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10" t="s">
-        <v>93</v>
+      <c r="C14" s="17"/>
+      <c r="D14" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14" s="17"/>
+      <c r="H14" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="K14" s="17"/>
+      <c r="L14" s="9" t="s">
+        <v>89</v>
       </c>
       <c r="N14" t="s">
         <v>25</v>
       </c>
-      <c r="O14" s="10"/>
-      <c r="P14" s="10" t="s">
+      <c r="O14" s="17"/>
+      <c r="P14" s="9" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="15" spans="2:19" x14ac:dyDescent="0.4">
+      <c r="C15" s="17"/>
+      <c r="D15" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G15" s="17"/>
+      <c r="H15" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="K15" s="17"/>
+      <c r="L15" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="O15" s="17"/>
+      <c r="P15" s="9" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="2:19" x14ac:dyDescent="0.4">
-      <c r="C15" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="D15" s="10" t="s">
+    <row r="16" spans="2:19" x14ac:dyDescent="0.4">
+      <c r="C16" s="17"/>
+      <c r="D16" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="G16" s="17"/>
+      <c r="H16" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="K16" s="17"/>
+      <c r="L16" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="O16" s="17"/>
+      <c r="P16" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.4">
+      <c r="C17" s="17"/>
+      <c r="D17" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="G17" s="17"/>
+      <c r="H17" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="K17" s="17"/>
+      <c r="L17" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="O17" s="17"/>
+      <c r="P17" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.4">
+      <c r="C18" s="17"/>
+      <c r="D18" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="G18" s="17"/>
+      <c r="H18" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K18" s="17"/>
+      <c r="L18" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="O18" s="17"/>
+      <c r="P18" s="10" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.4">
+      <c r="C19" s="17"/>
+      <c r="D19" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="G19" s="17"/>
+      <c r="H19" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="K19" s="17"/>
+      <c r="L19" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="O19" s="17"/>
+      <c r="P19" s="9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.4">
+      <c r="C20" s="17"/>
+      <c r="D20" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G20" s="17"/>
+      <c r="H20" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="K20" s="17"/>
+      <c r="L20" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="O20" s="16"/>
+      <c r="P20" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="G15" s="9"/>
-      <c r="H15" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="O15" s="10"/>
-      <c r="P15" s="10" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="16" spans="2:19" x14ac:dyDescent="0.4">
-      <c r="C16" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="G16" s="9"/>
-      <c r="H16" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="O16" s="10"/>
-      <c r="P16" s="10" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.4">
-      <c r="C17" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="D17" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="G17" s="9"/>
-      <c r="H17" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="O17" s="10"/>
-      <c r="P17" s="10" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.4">
-      <c r="C18" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="G18" s="9"/>
-      <c r="H18" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="O18" s="10"/>
-      <c r="P18" s="11" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.4">
-      <c r="C19" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="G19" s="9"/>
-      <c r="H19" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.4">
-      <c r="C20" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="G20" s="9"/>
-      <c r="H20" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10" t="s">
-        <v>123</v>
-      </c>
     </row>
     <row r="21" spans="3:16" x14ac:dyDescent="0.4">
-      <c r="C21" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="G21" s="9"/>
-      <c r="H21" s="10" t="s">
+      <c r="C21" s="17"/>
+      <c r="D21" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="G21" s="17"/>
+      <c r="H21" s="9" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="22" spans="3:16" x14ac:dyDescent="0.4">
-      <c r="C22" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="D22" s="10" t="s">
+      <c r="C22" s="17"/>
+      <c r="D22" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G22" s="9"/>
-      <c r="H22" s="10" t="s">
+      <c r="G22" s="17"/>
+      <c r="H22" s="9" t="s">
         <v>58</v>
       </c>
       <c r="J22" t="s">
         <v>61</v>
       </c>
-      <c r="K22" s="10"/>
-      <c r="L22" s="11" t="s">
-        <v>85</v>
+      <c r="K22" s="17"/>
+      <c r="L22" s="10" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="23" spans="3:16" x14ac:dyDescent="0.4">
-      <c r="C23" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="D23" s="16" t="s">
+      <c r="C23" s="17"/>
+      <c r="D23" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="G23" s="9"/>
-      <c r="H23" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="K23" s="10"/>
-      <c r="L23" s="14" t="s">
+      <c r="G23" s="17"/>
+      <c r="H23" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="K23" s="17"/>
+      <c r="L23" s="13" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="24" spans="3:16" x14ac:dyDescent="0.4">
-      <c r="C24" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="D24" s="11" t="s">
+      <c r="C24" s="17"/>
+      <c r="D24" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="G24" s="9"/>
-      <c r="H24" s="10" t="s">
+      <c r="G24" s="17"/>
+      <c r="H24" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="K24" s="10"/>
-      <c r="L24" s="10" t="s">
+      <c r="K24" s="17"/>
+      <c r="L24" s="9" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="25" spans="3:16" x14ac:dyDescent="0.4">
-      <c r="C25" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="G25" s="9"/>
-      <c r="H25" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="K25" s="10"/>
-      <c r="L25" s="10" t="s">
-        <v>100</v>
+      <c r="C25" s="17"/>
+      <c r="D25" s="9"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="K25" s="17"/>
+      <c r="L25" s="9" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="26" spans="3:16" x14ac:dyDescent="0.4">
-      <c r="G26" s="9"/>
-      <c r="H26" s="10" t="s">
+      <c r="G26" s="17"/>
+      <c r="H26" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="K26" s="10"/>
-      <c r="L26" s="11" t="s">
+      <c r="K26" s="17"/>
+      <c r="L26" s="10" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="27" spans="3:16" x14ac:dyDescent="0.4">
-      <c r="G27" s="9"/>
-      <c r="H27" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="K27" s="10"/>
-      <c r="L27" s="11" t="s">
-        <v>86</v>
+      <c r="G27" s="17"/>
+      <c r="H27" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="K27" s="17"/>
+      <c r="L27" s="9" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="3:16" x14ac:dyDescent="0.4">
-      <c r="G28" s="9"/>
-      <c r="H28" s="11" t="s">
-        <v>126</v>
+      <c r="G28" s="17"/>
+      <c r="H28" s="10" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
